--- a/data/raw/inventory/Week 19/White_Mulberry/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 19/White_Mulberry/Inventory Snapshot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 19\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE9523A-9B11-4917-B597-628251D4AC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D57F94-0584-4E5B-8C5A-6FAA687E57A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="201">
   <si>
     <t>SKU</t>
   </si>
@@ -637,6 +637,9 @@
   </si>
   <si>
     <t>B0DSG4F8D9</t>
+  </si>
+  <si>
+    <t>Open Order</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L135"/>
+  <dimension ref="A1:L138"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -3947,25 +3950,85 @@
       </c>
       <c r="K135" s="8"/>
     </row>
+    <row r="136" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C136" t="s">
+        <v>107</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I136" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C137" t="s">
+        <v>107</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I137" s="1">
+        <v>500</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C138" t="s">
+        <v>107</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I138" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A65:A123">
+    <cfRule type="duplicateValues" dxfId="7" priority="1587"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="7" priority="1353"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="6" priority="1564"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1565" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1564"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1565" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="4" priority="1351"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1352" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1351"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1352" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="2" priority="1349"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1350" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A65:A123">
-    <cfRule type="duplicateValues" dxfId="0" priority="1587"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1349"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1350" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
